--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18AB346-798B-404F-AB4E-818EA3E5553D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3CFD4-EA94-4426-BE48-3BCAD54B7870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,6 +788,12 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3CFD4-EA94-4426-BE48-3BCAD54B7870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A92B858-1138-4FA9-89D6-A50F1CA5CB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -811,6 +811,12 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A92B858-1138-4FA9-89D6-A50F1CA5CB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92CE88-836F-46DE-B508-B115CE94F929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -834,6 +834,12 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92CE88-836F-46DE-B508-B115CE94F929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAC9964-0793-4A9E-9E49-31E37EBE1E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -857,6 +857,12 @@
       <c r="E5" t="s">
         <v>21</v>
       </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAC9964-0793-4A9E-9E49-31E37EBE1E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C881E02-E57A-4088-8CEB-B6E5A0685FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -880,6 +880,12 @@
       <c r="E6" t="s">
         <v>24</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7">
@@ -896,6 +902,12 @@
       </c>
       <c r="E7" t="s">
         <v>28</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C881E02-E57A-4088-8CEB-B6E5A0685FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A02D7CD-3094-4FE1-918D-EA3FC90E04BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,6 +926,12 @@
       <c r="E8" t="s">
         <v>31</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9">
@@ -943,6 +949,12 @@
       <c r="E9" t="s">
         <v>34</v>
       </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10">
@@ -960,6 +972,12 @@
       <c r="E10" t="s">
         <v>38</v>
       </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11">
@@ -976,6 +994,12 @@
       </c>
       <c r="E11" t="s">
         <v>42</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A02D7CD-3094-4FE1-918D-EA3FC90E04BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215DAE1F-5CFC-4BCB-B73D-D44DCB4BD178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1018,6 +1018,12 @@
       <c r="E12" t="s">
         <v>45</v>
       </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13">
@@ -1035,6 +1041,12 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14">
@@ -1051,6 +1063,12 @@
       </c>
       <c r="E14" t="s">
         <v>52</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215DAE1F-5CFC-4BCB-B73D-D44DCB4BD178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3954C0E5-AEF3-4071-BFF1-C50050704B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="10457" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1087,6 +1087,12 @@
       <c r="E15" t="s">
         <v>56</v>
       </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16">
@@ -1104,8 +1110,14 @@
       <c r="E16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1121,8 +1133,14 @@
       <c r="E17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1138,8 +1156,14 @@
       <c r="E18" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1155,8 +1179,14 @@
       <c r="E19" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1172,8 +1202,14 @@
       <c r="E20" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1190,7 +1226,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1207,7 +1243,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1224,7 +1260,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1241,7 +1277,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1258,7 +1294,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1275,7 +1311,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1292,7 +1328,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1309,7 +1345,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1326,7 +1362,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1343,7 +1379,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1360,7 +1396,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3954C0E5-AEF3-4071-BFF1-C50050704B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F2DE44-D646-4530-A0BC-BCA05009AD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="10457" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1225,6 +1225,12 @@
       <c r="E21" t="s">
         <v>74</v>
       </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22">
@@ -1242,6 +1248,12 @@
       <c r="E22" t="s">
         <v>78</v>
       </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23">
@@ -1259,6 +1271,12 @@
       <c r="E23" t="s">
         <v>82</v>
       </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24">
@@ -1276,6 +1294,12 @@
       <c r="E24" t="s">
         <v>85</v>
       </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25">
@@ -1292,6 +1316,12 @@
       </c>
       <c r="E25" t="s">
         <v>88</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F2DE44-D646-4530-A0BC-BCA05009AD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBD9C8F-C208-4CA4-A4EC-3307B37007C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,12 +417,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -437,8 +443,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1340,6 +1347,12 @@
       <c r="E26" t="s">
         <v>89</v>
       </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27">
@@ -1357,6 +1370,12 @@
       <c r="E27" t="s">
         <v>90</v>
       </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28">
@@ -1374,6 +1393,12 @@
       <c r="E28" t="s">
         <v>91</v>
       </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29">
@@ -1391,6 +1416,12 @@
       <c r="E29" t="s">
         <v>92</v>
       </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30">
@@ -1405,8 +1436,14 @@
       <c r="D30" t="s">
         <v>32</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -1422,8 +1459,14 @@
       <c r="D31" t="s">
         <v>27</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>91</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -1441,6 +1484,12 @@
       </c>
       <c r="E32" t="s">
         <v>93</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBD9C8F-C208-4CA4-A4EC-3307B37007C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C4A3A1-BB36-4908-9814-2FBAF024FB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,9 +443,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1492,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1508,8 +1509,14 @@
       <c r="E33" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1525,8 +1532,14 @@
       <c r="E34" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1542,8 +1555,14 @@
       <c r="E35" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1559,8 +1578,14 @@
       <c r="E36" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1576,8 +1601,14 @@
       <c r="E37" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1593,8 +1624,14 @@
       <c r="E38" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1610,8 +1647,14 @@
       <c r="E39" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1627,8 +1670,14 @@
       <c r="E40" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1644,8 +1693,14 @@
       <c r="E41" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1662,7 +1717,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1679,7 +1734,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1696,7 +1751,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1713,7 +1768,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1730,7 +1785,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1747,7 +1802,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C4A3A1-BB36-4908-9814-2FBAF024FB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF82FFF-E342-4D85-9B25-0BFE0EEDF5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,7 +417,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +427,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -443,10 +449,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1716,6 +1723,12 @@
       <c r="E42" t="s">
         <v>103</v>
       </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43">
@@ -1733,6 +1746,12 @@
       <c r="E43" t="s">
         <v>104</v>
       </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44">
@@ -1750,6 +1769,12 @@
       <c r="E44" t="s">
         <v>105</v>
       </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45">
@@ -1767,22 +1792,34 @@
       <c r="E45" t="s">
         <v>106</v>
       </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A46">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="3" t="s">
         <v>107</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF82FFF-E342-4D85-9B25-0BFE0EEDF5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02537341-919F-4CD5-9A31-4EDBD829D263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1838,6 +1838,12 @@
       <c r="E47" t="s">
         <v>108</v>
       </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48">
@@ -1855,8 +1861,14 @@
       <c r="E48" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1872,8 +1884,14 @@
       <c r="E49" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1889,8 +1907,14 @@
       <c r="E50" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1906,8 +1930,14 @@
       <c r="E51" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1923,8 +1953,14 @@
       <c r="E52" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F52">
+        <v>4</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1940,8 +1976,14 @@
       <c r="E53" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1958,7 +2000,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1975,7 +2017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1992,7 +2034,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2009,7 +2051,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2026,7 +2068,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2043,7 +2085,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2060,7 +2102,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2077,7 +2119,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2094,7 +2136,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2111,7 +2153,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>63</v>
       </c>

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02537341-919F-4CD5-9A31-4EDBD829D263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECEF3B3-292C-4537-8CAC-3FF52B907FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1999,6 +1999,12 @@
       <c r="E54" t="s">
         <v>113</v>
       </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55">
@@ -2016,6 +2022,12 @@
       <c r="E55" t="s">
         <v>113</v>
       </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56">
@@ -2033,6 +2045,12 @@
       <c r="E56" t="s">
         <v>114</v>
       </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57">
@@ -2050,6 +2068,12 @@
       <c r="E57" t="s">
         <v>114</v>
       </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58">
@@ -2067,6 +2091,12 @@
       <c r="E58" t="s">
         <v>115</v>
       </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59">
@@ -2084,6 +2114,12 @@
       <c r="E59" t="s">
         <v>115</v>
       </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60">
@@ -2101,6 +2137,12 @@
       <c r="E60" t="s">
         <v>116</v>
       </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61">
@@ -2117,6 +2159,12 @@
       </c>
       <c r="E61" t="s">
         <v>116</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECEF3B3-292C-4537-8CAC-3FF52B907FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F880FAC-4765-428E-9740-52DD892747A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2183,6 +2183,12 @@
       <c r="E62" t="s">
         <v>117</v>
       </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63">
@@ -2200,6 +2206,12 @@
       <c r="E63" t="s">
         <v>117</v>
       </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64">
@@ -2217,8 +2229,14 @@
       <c r="E64" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2234,8 +2252,14 @@
       <c r="E65" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2251,8 +2275,14 @@
       <c r="E66" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2268,8 +2298,14 @@
       <c r="E67" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2286,7 +2322,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2303,7 +2339,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2320,7 +2356,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2337,7 +2373,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2354,7 +2390,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>72</v>
       </c>

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F880FAC-4765-428E-9740-52DD892747A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8BA914-168B-4E11-BF35-4A101B89C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2321,6 +2321,12 @@
       <c r="E68" t="s">
         <v>120</v>
       </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69">
@@ -2338,6 +2344,12 @@
       <c r="E69" t="s">
         <v>120</v>
       </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70">
@@ -2355,6 +2367,12 @@
       <c r="E70" t="s">
         <v>121</v>
       </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71">
@@ -2371,6 +2389,12 @@
       </c>
       <c r="E71" t="s">
         <v>121</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">

--- a/partidos.xlsx
+++ b/partidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8BA914-168B-4E11-BF35-4A101B89C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A5BAA9-21D4-4E8F-8B96-0830568C2012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2413,6 +2413,12 @@
       <c r="E72" t="s">
         <v>122</v>
       </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73">
@@ -2429,6 +2435,12 @@
       </c>
       <c r="E73" t="s">
         <v>122</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
